--- a/artfynd/A 37606-2023 artfynd.xlsx
+++ b/artfynd/A 37606-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118866765</v>
+        <v>118864962</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500381</v>
+        <v>500426</v>
       </c>
       <c r="R2" t="n">
-        <v>6807288</v>
+        <v>6807347</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118865723</v>
+        <v>118865910</v>
       </c>
       <c r="B3" t="n">
         <v>78484</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500415</v>
+        <v>500424</v>
       </c>
       <c r="R3" t="n">
-        <v>6807202</v>
+        <v>6807206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118864962</v>
+        <v>118865578</v>
       </c>
       <c r="B5" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500426</v>
+        <v>500411</v>
       </c>
       <c r="R5" t="n">
-        <v>6807347</v>
+        <v>6807287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118865699</v>
+        <v>118866913</v>
       </c>
       <c r="B6" t="n">
         <v>78484</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500423</v>
+        <v>500357</v>
       </c>
       <c r="R6" t="n">
-        <v>6807218</v>
+        <v>6807332</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118865341</v>
+        <v>118867066</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>91779</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500453</v>
+        <v>500335</v>
       </c>
       <c r="R7" t="n">
-        <v>6807301</v>
+        <v>6807383</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118865910</v>
+        <v>118865476</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>90524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500424</v>
+        <v>500455</v>
       </c>
       <c r="R8" t="n">
-        <v>6807206</v>
+        <v>6807263</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118866913</v>
+        <v>118866921</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500357</v>
+        <v>500352</v>
       </c>
       <c r="R9" t="n">
-        <v>6807332</v>
+        <v>6807340</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118865308</v>
+        <v>118865204</v>
       </c>
       <c r="B10" t="n">
         <v>78484</v>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500444</v>
+        <v>500449</v>
       </c>
       <c r="R10" t="n">
         <v>6807287</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118865009</v>
+        <v>118865699</v>
       </c>
       <c r="B11" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500443</v>
+        <v>500423</v>
       </c>
       <c r="R11" t="n">
-        <v>6807327</v>
+        <v>6807218</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118865082</v>
+        <v>118865723</v>
       </c>
       <c r="B12" t="n">
         <v>78484</v>
@@ -1731,14 +1731,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500423</v>
+        <v>500415</v>
       </c>
       <c r="R12" t="n">
-        <v>6807330</v>
+        <v>6807202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118867190</v>
+        <v>118867220</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>91791</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118867220</v>
+        <v>118865412</v>
       </c>
       <c r="B14" t="n">
-        <v>91791</v>
+        <v>78221</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,38 +1911,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500342</v>
+        <v>500453</v>
       </c>
       <c r="R14" t="n">
-        <v>6807374</v>
+        <v>6807287</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118865204</v>
+        <v>118864991</v>
       </c>
       <c r="B15" t="n">
         <v>78484</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500449</v>
+        <v>500453</v>
       </c>
       <c r="R15" t="n">
-        <v>6807287</v>
+        <v>6807328</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118865476</v>
+        <v>118866251</v>
       </c>
       <c r="B16" t="n">
-        <v>90524</v>
+        <v>80441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,34 +2119,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500455</v>
+        <v>500369</v>
       </c>
       <c r="R16" t="n">
-        <v>6807263</v>
+        <v>6807130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118866251</v>
+        <v>118865082</v>
       </c>
       <c r="B17" t="n">
-        <v>80441</v>
+        <v>78484</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,34 +2221,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500369</v>
+        <v>500423</v>
       </c>
       <c r="R17" t="n">
-        <v>6807130</v>
+        <v>6807330</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118866837</v>
+        <v>118864822</v>
       </c>
       <c r="B18" t="n">
         <v>78484</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500370</v>
+        <v>500406</v>
       </c>
       <c r="R18" t="n">
-        <v>6807329</v>
+        <v>6807352</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118865412</v>
+        <v>118866765</v>
       </c>
       <c r="B19" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500453</v>
+        <v>500381</v>
       </c>
       <c r="R19" t="n">
-        <v>6807287</v>
+        <v>6807288</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118865717</v>
+        <v>118866276</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500413</v>
+        <v>500369</v>
       </c>
       <c r="R20" t="n">
-        <v>6807213</v>
+        <v>6807130</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118865578</v>
+        <v>118865009</v>
       </c>
       <c r="B21" t="n">
-        <v>78221</v>
+        <v>90469</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500411</v>
+        <v>500443</v>
       </c>
       <c r="R21" t="n">
-        <v>6807287</v>
+        <v>6807327</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118864991</v>
+        <v>118867190</v>
       </c>
       <c r="B22" t="n">
         <v>78484</v>
@@ -2751,14 +2751,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500453</v>
+        <v>500342</v>
       </c>
       <c r="R22" t="n">
-        <v>6807328</v>
+        <v>6807374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118866921</v>
+        <v>118865373</v>
       </c>
       <c r="B23" t="n">
-        <v>79073</v>
+        <v>8416</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,38 +2829,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500352</v>
+        <v>500458</v>
       </c>
       <c r="R23" t="n">
-        <v>6807340</v>
+        <v>6807259</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118867066</v>
+        <v>118866837</v>
       </c>
       <c r="B24" t="n">
-        <v>91779</v>
+        <v>78484</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,38 +2936,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500335</v>
+        <v>500370</v>
       </c>
       <c r="R24" t="n">
-        <v>6807383</v>
+        <v>6807329</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3026,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118864822</v>
+        <v>118865308</v>
       </c>
       <c r="B25" t="n">
         <v>78484</v>
@@ -3061,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500406</v>
+        <v>500444</v>
       </c>
       <c r="R25" t="n">
-        <v>6807352</v>
+        <v>6807287</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118865373</v>
+        <v>118865341</v>
       </c>
       <c r="B26" t="n">
-        <v>8416</v>
+        <v>78484</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3135,43 +3140,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500458</v>
+        <v>500453</v>
       </c>
       <c r="R26" t="n">
-        <v>6807259</v>
+        <v>6807301</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118866276</v>
+        <v>118866975</v>
       </c>
       <c r="B27" t="n">
-        <v>78221</v>
+        <v>91779</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,38 +3242,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500369</v>
+        <v>500343</v>
       </c>
       <c r="R27" t="n">
-        <v>6807130</v>
+        <v>6807365</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118866975</v>
+        <v>118865717</v>
       </c>
       <c r="B28" t="n">
-        <v>91779</v>
+        <v>78484</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,38 +3344,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500343</v>
+        <v>500413</v>
       </c>
       <c r="R28" t="n">
-        <v>6807365</v>
+        <v>6807213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 37606-2023 artfynd.xlsx
+++ b/artfynd/A 37606-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118864962</v>
+        <v>118866913</v>
       </c>
       <c r="B2" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500426</v>
+        <v>500357</v>
       </c>
       <c r="R2" t="n">
-        <v>6807347</v>
+        <v>6807332</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118865910</v>
+        <v>118867220</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>91791</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500424</v>
+        <v>500342</v>
       </c>
       <c r="R3" t="n">
-        <v>6807206</v>
+        <v>6807374</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118867181</v>
+        <v>118865308</v>
       </c>
       <c r="B4" t="n">
-        <v>90524</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500342</v>
+        <v>500444</v>
       </c>
       <c r="R4" t="n">
-        <v>6807374</v>
+        <v>6807287</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118865578</v>
+        <v>118865910</v>
       </c>
       <c r="B5" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500411</v>
+        <v>500424</v>
       </c>
       <c r="R5" t="n">
-        <v>6807287</v>
+        <v>6807206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118866913</v>
+        <v>118865373</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>8416</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500357</v>
+        <v>500458</v>
       </c>
       <c r="R6" t="n">
-        <v>6807332</v>
+        <v>6807259</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118867066</v>
+        <v>118864962</v>
       </c>
       <c r="B7" t="n">
-        <v>91779</v>
+        <v>79073</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1202,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500335</v>
+        <v>500426</v>
       </c>
       <c r="R7" t="n">
-        <v>6807383</v>
+        <v>6807347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118865476</v>
+        <v>118866276</v>
       </c>
       <c r="B8" t="n">
-        <v>90524</v>
+        <v>78221</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,34 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500455</v>
+        <v>500369</v>
       </c>
       <c r="R8" t="n">
-        <v>6807263</v>
+        <v>6807130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118866921</v>
+        <v>118865082</v>
       </c>
       <c r="B9" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1410,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500352</v>
+        <v>500423</v>
       </c>
       <c r="R9" t="n">
-        <v>6807340</v>
+        <v>6807330</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118865204</v>
+        <v>118866251</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>80441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1512,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500449</v>
+        <v>500369</v>
       </c>
       <c r="R10" t="n">
-        <v>6807287</v>
+        <v>6807130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118865699</v>
+        <v>118866975</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>91779</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1610,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500423</v>
+        <v>500343</v>
       </c>
       <c r="R11" t="n">
-        <v>6807218</v>
+        <v>6807365</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118865723</v>
+        <v>118867181</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>90524</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,34 +1716,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500415</v>
+        <v>500342</v>
       </c>
       <c r="R12" t="n">
-        <v>6807202</v>
+        <v>6807374</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118867220</v>
+        <v>118865699</v>
       </c>
       <c r="B13" t="n">
-        <v>91791</v>
+        <v>78484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,38 +1814,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500342</v>
+        <v>500423</v>
       </c>
       <c r="R13" t="n">
-        <v>6807374</v>
+        <v>6807218</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118865412</v>
+        <v>118867066</v>
       </c>
       <c r="B14" t="n">
-        <v>78221</v>
+        <v>91779</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,38 +1916,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500453</v>
+        <v>500335</v>
       </c>
       <c r="R14" t="n">
-        <v>6807287</v>
+        <v>6807383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118864991</v>
+        <v>118865009</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500453</v>
+        <v>500443</v>
       </c>
       <c r="R15" t="n">
-        <v>6807328</v>
+        <v>6807327</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118866251</v>
+        <v>118865476</v>
       </c>
       <c r="B16" t="n">
-        <v>80441</v>
+        <v>90524</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,34 +2124,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500369</v>
+        <v>500455</v>
       </c>
       <c r="R16" t="n">
-        <v>6807130</v>
+        <v>6807263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118865082</v>
+        <v>118865717</v>
       </c>
       <c r="B17" t="n">
         <v>78484</v>
@@ -2241,14 +2246,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500423</v>
+        <v>500413</v>
       </c>
       <c r="R17" t="n">
-        <v>6807330</v>
+        <v>6807213</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118864822</v>
+        <v>118865578</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500406</v>
+        <v>500411</v>
       </c>
       <c r="R18" t="n">
-        <v>6807352</v>
+        <v>6807287</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2414,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118866765</v>
+        <v>118864991</v>
       </c>
       <c r="B19" t="n">
         <v>78484</v>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500381</v>
+        <v>500453</v>
       </c>
       <c r="R19" t="n">
-        <v>6807288</v>
+        <v>6807328</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118866276</v>
+        <v>118866837</v>
       </c>
       <c r="B20" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,34 +2532,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500369</v>
+        <v>500370</v>
       </c>
       <c r="R20" t="n">
-        <v>6807130</v>
+        <v>6807329</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118865009</v>
+        <v>118866765</v>
       </c>
       <c r="B21" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500443</v>
+        <v>500381</v>
       </c>
       <c r="R21" t="n">
-        <v>6807327</v>
+        <v>6807288</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118867190</v>
+        <v>118866921</v>
       </c>
       <c r="B22" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500342</v>
+        <v>500352</v>
       </c>
       <c r="R22" t="n">
-        <v>6807374</v>
+        <v>6807340</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118865373</v>
+        <v>118865204</v>
       </c>
       <c r="B23" t="n">
-        <v>8416</v>
+        <v>78484</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,43 +2834,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500458</v>
+        <v>500449</v>
       </c>
       <c r="R23" t="n">
-        <v>6807259</v>
+        <v>6807287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,7 +2924,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118866837</v>
+        <v>118865341</v>
       </c>
       <c r="B24" t="n">
         <v>78484</v>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500370</v>
+        <v>500453</v>
       </c>
       <c r="R24" t="n">
-        <v>6807329</v>
+        <v>6807301</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118865308</v>
+        <v>118864822</v>
       </c>
       <c r="B25" t="n">
         <v>78484</v>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500444</v>
+        <v>500406</v>
       </c>
       <c r="R25" t="n">
-        <v>6807287</v>
+        <v>6807352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118865341</v>
+        <v>118865412</v>
       </c>
       <c r="B26" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3171,7 +3171,7 @@
         <v>500453</v>
       </c>
       <c r="R26" t="n">
-        <v>6807301</v>
+        <v>6807287</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118866975</v>
+        <v>118865723</v>
       </c>
       <c r="B27" t="n">
-        <v>91779</v>
+        <v>78484</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,38 +3242,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500343</v>
+        <v>500415</v>
       </c>
       <c r="R27" t="n">
-        <v>6807365</v>
+        <v>6807202</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118865717</v>
+        <v>118867190</v>
       </c>
       <c r="B28" t="n">
         <v>78484</v>
@@ -3368,14 +3368,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500413</v>
+        <v>500342</v>
       </c>
       <c r="R28" t="n">
-        <v>6807213</v>
+        <v>6807374</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 37606-2023 artfynd.xlsx
+++ b/artfynd/A 37606-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118866913</v>
+        <v>118866921</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>79080</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500357</v>
+        <v>500352</v>
       </c>
       <c r="R2" t="n">
-        <v>6807332</v>
+        <v>6807340</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118867220</v>
+        <v>118865578</v>
       </c>
       <c r="B3" t="n">
-        <v>91791</v>
+        <v>78228</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500342</v>
+        <v>500411</v>
       </c>
       <c r="R3" t="n">
-        <v>6807374</v>
+        <v>6807287</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118865308</v>
+        <v>118866276</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>78228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500444</v>
+        <v>500369</v>
       </c>
       <c r="R4" t="n">
-        <v>6807287</v>
+        <v>6807130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118865910</v>
+        <v>118867066</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>91786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500424</v>
+        <v>500335</v>
       </c>
       <c r="R5" t="n">
-        <v>6807206</v>
+        <v>6807383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118865373</v>
+        <v>118865412</v>
       </c>
       <c r="B6" t="n">
-        <v>8416</v>
+        <v>78228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,43 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500458</v>
+        <v>500453</v>
       </c>
       <c r="R6" t="n">
-        <v>6807259</v>
+        <v>6807287</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118864962</v>
+        <v>118866837</v>
       </c>
       <c r="B7" t="n">
-        <v>79073</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500426</v>
+        <v>500370</v>
       </c>
       <c r="R7" t="n">
-        <v>6807347</v>
+        <v>6807329</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118866276</v>
+        <v>118865717</v>
       </c>
       <c r="B8" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500369</v>
+        <v>500413</v>
       </c>
       <c r="R8" t="n">
-        <v>6807130</v>
+        <v>6807213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118865082</v>
+        <v>118865699</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,14 +1425,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>500423</v>
       </c>
       <c r="R9" t="n">
-        <v>6807330</v>
+        <v>6807218</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118866251</v>
+        <v>118865204</v>
       </c>
       <c r="B10" t="n">
-        <v>80441</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,34 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500369</v>
+        <v>500449</v>
       </c>
       <c r="R10" t="n">
-        <v>6807130</v>
+        <v>6807287</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118866975</v>
+        <v>118864991</v>
       </c>
       <c r="B11" t="n">
-        <v>91779</v>
+        <v>78491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500343</v>
+        <v>500453</v>
       </c>
       <c r="R11" t="n">
-        <v>6807365</v>
+        <v>6807328</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118867181</v>
+        <v>118865476</v>
       </c>
       <c r="B12" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,14 +1731,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500342</v>
+        <v>500455</v>
       </c>
       <c r="R12" t="n">
-        <v>6807374</v>
+        <v>6807263</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118865699</v>
+        <v>118867220</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>91798</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,38 +1809,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500423</v>
+        <v>500342</v>
       </c>
       <c r="R13" t="n">
-        <v>6807218</v>
+        <v>6807374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118867066</v>
+        <v>118865723</v>
       </c>
       <c r="B14" t="n">
-        <v>91779</v>
+        <v>78491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,38 +1911,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500335</v>
+        <v>500415</v>
       </c>
       <c r="R14" t="n">
-        <v>6807383</v>
+        <v>6807202</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118865009</v>
+        <v>118866765</v>
       </c>
       <c r="B15" t="n">
-        <v>90469</v>
+        <v>78491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500443</v>
+        <v>500381</v>
       </c>
       <c r="R15" t="n">
-        <v>6807327</v>
+        <v>6807288</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118865476</v>
+        <v>118865009</v>
       </c>
       <c r="B16" t="n">
-        <v>90524</v>
+        <v>90476</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500455</v>
+        <v>500443</v>
       </c>
       <c r="R16" t="n">
-        <v>6807263</v>
+        <v>6807327</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118865717</v>
+        <v>118865910</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500413</v>
+        <v>500424</v>
       </c>
       <c r="R17" t="n">
-        <v>6807213</v>
+        <v>6807206</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118865578</v>
+        <v>118865341</v>
       </c>
       <c r="B18" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500411</v>
+        <v>500453</v>
       </c>
       <c r="R18" t="n">
-        <v>6807287</v>
+        <v>6807301</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118864991</v>
+        <v>118865373</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
+        <v>8416</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,38 +2421,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500453</v>
+        <v>500458</v>
       </c>
       <c r="R19" t="n">
-        <v>6807328</v>
+        <v>6807259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118866837</v>
+        <v>118865308</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500370</v>
+        <v>500444</v>
       </c>
       <c r="R20" t="n">
-        <v>6807329</v>
+        <v>6807287</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118866765</v>
+        <v>118864962</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>79080</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500381</v>
+        <v>500426</v>
       </c>
       <c r="R21" t="n">
-        <v>6807288</v>
+        <v>6807347</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118866921</v>
+        <v>118867181</v>
       </c>
       <c r="B22" t="n">
-        <v>79073</v>
+        <v>90531</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500352</v>
+        <v>500342</v>
       </c>
       <c r="R22" t="n">
-        <v>6807340</v>
+        <v>6807374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118865204</v>
+        <v>118867190</v>
       </c>
       <c r="B23" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,14 +2858,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500449</v>
+        <v>500342</v>
       </c>
       <c r="R23" t="n">
-        <v>6807287</v>
+        <v>6807374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118865341</v>
+        <v>118865082</v>
       </c>
       <c r="B24" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500453</v>
+        <v>500423</v>
       </c>
       <c r="R24" t="n">
-        <v>6807301</v>
+        <v>6807330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,7 +3029,7 @@
         <v>118864822</v>
       </c>
       <c r="B25" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118865412</v>
+        <v>118866913</v>
       </c>
       <c r="B26" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500453</v>
+        <v>500357</v>
       </c>
       <c r="R26" t="n">
-        <v>6807287</v>
+        <v>6807332</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118865723</v>
+        <v>118866975</v>
       </c>
       <c r="B27" t="n">
-        <v>78484</v>
+        <v>91786</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,38 +3242,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500415</v>
+        <v>500343</v>
       </c>
       <c r="R27" t="n">
-        <v>6807202</v>
+        <v>6807365</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118867190</v>
+        <v>118866251</v>
       </c>
       <c r="B28" t="n">
-        <v>78484</v>
+        <v>80448</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,34 +3348,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500342</v>
+        <v>500369</v>
       </c>
       <c r="R28" t="n">
-        <v>6807374</v>
+        <v>6807130</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 37606-2023 artfynd.xlsx
+++ b/artfynd/A 37606-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118866921</v>
+        <v>118865578</v>
       </c>
       <c r="B2" t="n">
-        <v>79080</v>
+        <v>78228</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500352</v>
+        <v>500411</v>
       </c>
       <c r="R2" t="n">
-        <v>6807340</v>
+        <v>6807287</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118865578</v>
+        <v>118866921</v>
       </c>
       <c r="B3" t="n">
-        <v>78228</v>
+        <v>79080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500411</v>
+        <v>500352</v>
       </c>
       <c r="R3" t="n">
-        <v>6807287</v>
+        <v>6807340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118867066</v>
+        <v>118865412</v>
       </c>
       <c r="B5" t="n">
-        <v>91786</v>
+        <v>78228</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500335</v>
+        <v>500453</v>
       </c>
       <c r="R5" t="n">
-        <v>6807383</v>
+        <v>6807287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118865412</v>
+        <v>118867066</v>
       </c>
       <c r="B6" t="n">
-        <v>78228</v>
+        <v>91786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500453</v>
+        <v>500335</v>
       </c>
       <c r="R6" t="n">
-        <v>6807287</v>
+        <v>6807383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118865308</v>
+        <v>118864962</v>
       </c>
       <c r="B20" t="n">
-        <v>78491</v>
+        <v>79080</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500444</v>
+        <v>500426</v>
       </c>
       <c r="R20" t="n">
-        <v>6807287</v>
+        <v>6807347</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118864962</v>
+        <v>118865308</v>
       </c>
       <c r="B21" t="n">
-        <v>79080</v>
+        <v>78491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500426</v>
+        <v>500444</v>
       </c>
       <c r="R21" t="n">
-        <v>6807347</v>
+        <v>6807287</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 37606-2023 artfynd.xlsx
+++ b/artfynd/A 37606-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118865578</v>
+        <v>118865082</v>
       </c>
       <c r="B2" t="n">
-        <v>78228</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500411</v>
+        <v>500423</v>
       </c>
       <c r="R2" t="n">
-        <v>6807287</v>
+        <v>6807330</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118866921</v>
+        <v>118864991</v>
       </c>
       <c r="B3" t="n">
-        <v>79080</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500352</v>
+        <v>500453</v>
       </c>
       <c r="R3" t="n">
-        <v>6807340</v>
+        <v>6807328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118866276</v>
+        <v>118866251</v>
       </c>
       <c r="B4" t="n">
-        <v>78228</v>
+        <v>80448</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118865412</v>
+        <v>118866975</v>
       </c>
       <c r="B5" t="n">
-        <v>78228</v>
+        <v>91786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500453</v>
+        <v>500343</v>
       </c>
       <c r="R5" t="n">
-        <v>6807287</v>
+        <v>6807365</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118867066</v>
+        <v>118865341</v>
       </c>
       <c r="B6" t="n">
-        <v>91786</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500335</v>
+        <v>500453</v>
       </c>
       <c r="R6" t="n">
-        <v>6807383</v>
+        <v>6807301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118866837</v>
+        <v>118867190</v>
       </c>
       <c r="B7" t="n">
         <v>78491</v>
@@ -1221,14 +1221,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500370</v>
+        <v>500342</v>
       </c>
       <c r="R7" t="n">
-        <v>6807329</v>
+        <v>6807374</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118865717</v>
+        <v>118867066</v>
       </c>
       <c r="B8" t="n">
-        <v>78491</v>
+        <v>91786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500413</v>
+        <v>500335</v>
       </c>
       <c r="R8" t="n">
-        <v>6807213</v>
+        <v>6807383</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118865699</v>
+        <v>118866921</v>
       </c>
       <c r="B9" t="n">
-        <v>78491</v>
+        <v>79080</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500423</v>
+        <v>500352</v>
       </c>
       <c r="R9" t="n">
-        <v>6807218</v>
+        <v>6807340</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118865204</v>
+        <v>118865412</v>
       </c>
       <c r="B10" t="n">
-        <v>78491</v>
+        <v>78228</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500449</v>
+        <v>500453</v>
       </c>
       <c r="R10" t="n">
         <v>6807287</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118864991</v>
+        <v>118866765</v>
       </c>
       <c r="B11" t="n">
         <v>78491</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500453</v>
+        <v>500381</v>
       </c>
       <c r="R11" t="n">
-        <v>6807328</v>
+        <v>6807288</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118865476</v>
+        <v>118865204</v>
       </c>
       <c r="B12" t="n">
-        <v>90531</v>
+        <v>78491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500455</v>
+        <v>500449</v>
       </c>
       <c r="R12" t="n">
-        <v>6807263</v>
+        <v>6807287</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118867220</v>
+        <v>118865723</v>
       </c>
       <c r="B13" t="n">
-        <v>91798</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,38 +1809,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500342</v>
+        <v>500415</v>
       </c>
       <c r="R13" t="n">
-        <v>6807374</v>
+        <v>6807202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118865723</v>
+        <v>118866913</v>
       </c>
       <c r="B14" t="n">
         <v>78491</v>
@@ -1935,14 +1935,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500415</v>
+        <v>500357</v>
       </c>
       <c r="R14" t="n">
-        <v>6807202</v>
+        <v>6807332</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118866765</v>
+        <v>118865578</v>
       </c>
       <c r="B15" t="n">
-        <v>78491</v>
+        <v>78228</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500381</v>
+        <v>500411</v>
       </c>
       <c r="R15" t="n">
-        <v>6807288</v>
+        <v>6807287</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118865009</v>
+        <v>118866276</v>
       </c>
       <c r="B16" t="n">
-        <v>90476</v>
+        <v>78228</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,38 +2115,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500443</v>
+        <v>500369</v>
       </c>
       <c r="R16" t="n">
-        <v>6807327</v>
+        <v>6807130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118865910</v>
+        <v>118867220</v>
       </c>
       <c r="B17" t="n">
-        <v>78491</v>
+        <v>91798</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,38 +2217,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500424</v>
+        <v>500342</v>
       </c>
       <c r="R17" t="n">
-        <v>6807206</v>
+        <v>6807374</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118865341</v>
+        <v>118864822</v>
       </c>
       <c r="B18" t="n">
         <v>78491</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500453</v>
+        <v>500406</v>
       </c>
       <c r="R18" t="n">
-        <v>6807301</v>
+        <v>6807352</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118865373</v>
+        <v>118865476</v>
       </c>
       <c r="B19" t="n">
-        <v>8416</v>
+        <v>90531</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,43 +2421,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500458</v>
+        <v>500455</v>
       </c>
       <c r="R19" t="n">
-        <v>6807259</v>
+        <v>6807263</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118864962</v>
+        <v>118865009</v>
       </c>
       <c r="B20" t="n">
-        <v>79080</v>
+        <v>90476</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500426</v>
+        <v>500443</v>
       </c>
       <c r="R20" t="n">
-        <v>6807347</v>
+        <v>6807327</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118865308</v>
+        <v>118865717</v>
       </c>
       <c r="B21" t="n">
         <v>78491</v>
@@ -2654,14 +2649,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500444</v>
+        <v>500413</v>
       </c>
       <c r="R21" t="n">
-        <v>6807287</v>
+        <v>6807213</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118867181</v>
+        <v>118864962</v>
       </c>
       <c r="B22" t="n">
-        <v>90531</v>
+        <v>79080</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,34 +2731,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500342</v>
+        <v>500426</v>
       </c>
       <c r="R22" t="n">
-        <v>6807374</v>
+        <v>6807347</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118867190</v>
+        <v>118865308</v>
       </c>
       <c r="B23" t="n">
         <v>78491</v>
@@ -2858,14 +2853,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500342</v>
+        <v>500444</v>
       </c>
       <c r="R23" t="n">
-        <v>6807374</v>
+        <v>6807287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118865082</v>
+        <v>118866837</v>
       </c>
       <c r="B24" t="n">
         <v>78491</v>
@@ -2964,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500423</v>
+        <v>500370</v>
       </c>
       <c r="R24" t="n">
-        <v>6807330</v>
+        <v>6807329</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118864822</v>
+        <v>118865373</v>
       </c>
       <c r="B25" t="n">
-        <v>78491</v>
+        <v>8416</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,38 +3033,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stormyren (Stormyren), Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500406</v>
+        <v>500458</v>
       </c>
       <c r="R25" t="n">
-        <v>6807352</v>
+        <v>6807259</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118866913</v>
+        <v>118865699</v>
       </c>
       <c r="B26" t="n">
         <v>78491</v>
@@ -3164,14 +3164,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stormyren (Stormyren), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500357</v>
+        <v>500423</v>
       </c>
       <c r="R26" t="n">
-        <v>6807332</v>
+        <v>6807218</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118866975</v>
+        <v>118865910</v>
       </c>
       <c r="B27" t="n">
-        <v>91786</v>
+        <v>78491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,38 +3242,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+          <t>Skäftdammen (Skäftdammen), Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500343</v>
+        <v>500424</v>
       </c>
       <c r="R27" t="n">
-        <v>6807365</v>
+        <v>6807206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118866251</v>
+        <v>118867181</v>
       </c>
       <c r="B28" t="n">
-        <v>80448</v>
+        <v>90531</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,34 +3348,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skäftdammen (Skäftdammen), Dlr</t>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500369</v>
+        <v>500342</v>
       </c>
       <c r="R28" t="n">
-        <v>6807130</v>
+        <v>6807374</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
